--- a/public/Assets/templates/oem-product-excel.xlsx
+++ b/public/Assets/templates/oem-product-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mirak\Downloads\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\FinayoApp-uat\public\Assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFDEE8B-4F6B-43F0-854B-F2D1F2542663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63336698-182F-46DC-84BF-296977C38C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>battery_type</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>E-Auto (L5)</t>
+  </si>
+  <si>
+    <t>approve_multi</t>
   </si>
 </sst>
 </file>
@@ -398,27 +401,28 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y2"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
     <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.88671875" customWidth="1"/>
-    <col min="14" max="14" width="4.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.36328125" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" customWidth="1"/>
+    <col min="9" max="9" width="14.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="16.90625" customWidth="1"/>
+    <col min="14" max="14" width="4.6328125" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -479,7 +483,9 @@
       <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
@@ -546,6 +552,9 @@
       <c r="T2" t="s">
         <v>25</v>
       </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
